--- a/data/output/evaluasi_53.xlsx
+++ b/data/output/evaluasi_53.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
